--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/CALIFORNIA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/CALIFORNIA_2020.xlsx
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Montecristo De Guerero</t>
+          <t>Montecristo De Guerrero</t>
         </is>
       </c>
       <c r="C85">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C157">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Praxedis G. Guerero</t>
+          <t>Praxedis G. Guerrero</t>
         </is>
       </c>
       <c r="C176">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C195">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C248">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C279">
@@ -5737,7 +5737,7 @@
         <v>136</v>
       </c>
       <c r="D299">
-        <v>0.0009580568353128479</v>
+        <v>0.000958056835312848</v>
       </c>
     </row>
     <row r="300">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C357">
@@ -7440,7 +7440,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C394">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C405">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C415">
@@ -8779,7 +8779,7 @@
         <v>128</v>
       </c>
       <c r="D468">
-        <v>0.0009017005508826803</v>
+        <v>0.0009017005508826804</v>
       </c>
     </row>
     <row r="469">
@@ -8977,7 +8977,7 @@
         <v>131</v>
       </c>
       <c r="D479">
-        <v>0.0009228341575439931</v>
+        <v>0.0009228341575439932</v>
       </c>
     </row>
     <row r="480">
@@ -9175,7 +9175,7 @@
         <v>136</v>
       </c>
       <c r="D490">
-        <v>0.0009580568353128479</v>
+        <v>0.000958056835312848</v>
       </c>
     </row>
     <row r="491">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C512">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C580">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C586">
@@ -11551,7 +11551,7 @@
         <v>134</v>
       </c>
       <c r="D622">
-        <v>0.0009439677642053059</v>
+        <v>0.000943967764205306</v>
       </c>
     </row>
     <row r="623">
@@ -11821,7 +11821,7 @@
         <v>128</v>
       </c>
       <c r="D637">
-        <v>0.0009017005508826803</v>
+        <v>0.0009017005508826804</v>
       </c>
     </row>
     <row r="638">
@@ -13344,7 +13344,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C722">
@@ -13531,7 +13531,7 @@
         <v>134</v>
       </c>
       <c r="D732">
-        <v>0.0009439677642053059</v>
+        <v>0.000943967764205306</v>
       </c>
     </row>
     <row r="733">
@@ -13675,7 +13675,7 @@
         <v>136</v>
       </c>
       <c r="D740">
-        <v>0.0009580568353128479</v>
+        <v>0.000958056835312848</v>
       </c>
     </row>
     <row r="741">
@@ -13819,7 +13819,7 @@
         <v>135</v>
       </c>
       <c r="D748">
-        <v>0.0009510122997590769</v>
+        <v>0.0009510122997590768</v>
       </c>
     </row>
     <row r="749">
@@ -14251,7 +14251,7 @@
         <v>135</v>
       </c>
       <c r="D772">
-        <v>0.0009510122997590769</v>
+        <v>0.0009510122997590768</v>
       </c>
     </row>
     <row r="773">
@@ -14395,7 +14395,7 @@
         <v>129</v>
       </c>
       <c r="D780">
-        <v>0.0009087450864364513</v>
+        <v>0.0009087450864364512</v>
       </c>
     </row>
     <row r="781">
@@ -14755,7 +14755,7 @@
         <v>135</v>
       </c>
       <c r="D800">
-        <v>0.0009510122997590769</v>
+        <v>0.0009510122997590768</v>
       </c>
     </row>
     <row r="801">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C906">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C945">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C994">
@@ -19021,7 +19021,7 @@
         <v>138</v>
       </c>
       <c r="D1037">
-        <v>0.0009721459064203897</v>
+        <v>0.0009721459064203896</v>
       </c>
     </row>
     <row r="1038">
@@ -19032,7 +19032,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>San Bartolome Yucane</t>
+          <t>San Bartolome Yucuane</t>
         </is>
       </c>
       <c r="C1038">
@@ -19219,7 +19219,7 @@
         <v>138</v>
       </c>
       <c r="D1048">
-        <v>0.0009721459064203897</v>
+        <v>0.0009721459064203896</v>
       </c>
     </row>
     <row r="1049">
@@ -20562,7 +20562,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1123">
@@ -20580,7 +20580,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1124">
@@ -22218,7 +22218,7 @@
       </c>
       <c r="B1215" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1215">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1216">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="B1228" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1228">
@@ -24583,7 +24583,7 @@
         <v>138</v>
       </c>
       <c r="D1346">
-        <v>0.0009721459064203897</v>
+        <v>0.0009721459064203896</v>
       </c>
     </row>
     <row r="1347">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="B1392" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1392">
@@ -26178,7 +26178,7 @@
       </c>
       <c r="B1435" t="inlineStr">
         <is>
-          <t>Yutanduchi De Guerero</t>
+          <t>Yutanduchi De Guerrero</t>
         </is>
       </c>
       <c r="C1435">
@@ -26311,7 +26311,7 @@
         <v>136</v>
       </c>
       <c r="D1442">
-        <v>0.0009580568353128479</v>
+        <v>0.000958056835312848</v>
       </c>
     </row>
     <row r="1443">
@@ -26718,7 +26718,7 @@
       </c>
       <c r="B1465" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C1465">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="B1519" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C1519">
@@ -28561,7 +28561,7 @@
         <v>134</v>
       </c>
       <c r="D1567">
-        <v>0.0009439677642053059</v>
+        <v>0.000943967764205306</v>
       </c>
     </row>
     <row r="1568">
@@ -29083,7 +29083,7 @@
         <v>131</v>
       </c>
       <c r="D1596">
-        <v>0.0009228341575439931</v>
+        <v>0.0009228341575439932</v>
       </c>
     </row>
     <row r="1597">
@@ -29562,7 +29562,7 @@
       </c>
       <c r="B1623" t="inlineStr">
         <is>
-          <t>Totoltepec De Guerero</t>
+          <t>Totoltepec De Guerrero</t>
         </is>
       </c>
       <c r="C1623">
@@ -29652,7 +29652,7 @@
       </c>
       <c r="B1628" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C1628">
@@ -30073,7 +30073,7 @@
         <v>138</v>
       </c>
       <c r="D1651">
-        <v>0.0009721459064203897</v>
+        <v>0.0009721459064203896</v>
       </c>
     </row>
     <row r="1652">
@@ -30937,7 +30937,7 @@
         <v>138</v>
       </c>
       <c r="D1699">
-        <v>0.0009721459064203897</v>
+        <v>0.0009721459064203896</v>
       </c>
     </row>
     <row r="1700">
@@ -31603,7 +31603,7 @@
         <v>134</v>
       </c>
       <c r="D1736">
-        <v>0.0009439677642053059</v>
+        <v>0.000943967764205306</v>
       </c>
     </row>
     <row r="1737">
@@ -33522,7 +33522,7 @@
       </c>
       <c r="B1843" t="inlineStr">
         <is>
-          <t>Amaxac De Guerero</t>
+          <t>Amaxac De Guerrero</t>
         </is>
       </c>
       <c r="C1843">
@@ -34249,7 +34249,7 @@
         <v>134</v>
       </c>
       <c r="D1883">
-        <v>0.0009439677642053059</v>
+        <v>0.000943967764205306</v>
       </c>
     </row>
     <row r="1884">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="B1892" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1892">
